--- a/public/unit_upload_template.xlsx
+++ b/public/unit_upload_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\lenaAI\lenaai-website\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D76F715-5229-442D-A8E9-5C5759648CB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD1EA71-7A35-4B4B-8395-376E14F01C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2484" yWindow="2484" windowWidth="22656" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2832" yWindow="2832" windowWidth="22656" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Units Template" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="62">
   <si>
     <t>buildingType</t>
   </si>
@@ -194,12 +194,6 @@
   </si>
   <si>
     <t>pp2_installment_amount_yearly</t>
-  </si>
-  <si>
-    <t>https://api.lenaai.net/images/develop_e2025c17, https://api.lenaai.net/images/develop_e2025c17</t>
-  </si>
-  <si>
-    <t>https://api.lenaai.net/images/develop_e2025c17</t>
   </si>
   <si>
     <t>pp5_price2</t>
@@ -363,964 +357,964 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -1498,37 +1492,37 @@
   <autoFilter ref="A1:AF4" xr:uid="{7D483870-0148-4BE6-BADA-FF58BC551527}"/>
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{88787F94-FFA1-4CD4-A028-46C60D04E42B}" name="buildingType" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{39A43C69-BA8F-471A-820B-7634B6C00857}" name="project" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{FA20424E-B41B-418D-B6E2-BC001D54AF24}" name="project_ar" dataDxfId="0"/>
-    <tableColumn id="4" xr3:uid="{92AA78DB-91CF-4E52-AE17-54AF20AA84F3}" name="view" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{C686F568-A904-4F0F-B54B-0D41263C91E9}" name="phase" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{06DE9C09-9D66-4E84-8BFA-9250BFABA13D}" name="city" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{7C4AD4EF-299B-4722-8957-3F8D28742DEA}" name="district" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{C10A1A14-7EC1-45BC-9552-8A98401737DB}" name="developer" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{D8E6284D-A3D8-40F8-945D-91573DB99A46}" name="unitTitle" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{DF08E38D-EE22-40B8-B49B-AE8CFB132491}" name="deliveryStatus" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{8D57A761-E792-4EC1-8B0A-31C4AC71E587}" name="bathroomCount" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{4E64BA77-CE3B-4387-9005-D07472224E91}" name="floor" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{F3C7A4FD-240B-49B6-A0A9-F75B071F140D}" name="roomsCount" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{56F4F824-2572-46E3-8D06-031BA4492E81}" name="landArea" dataDxfId="21"/>
-    <tableColumn id="15" xr3:uid="{013500D4-906E-4C51-A6FC-49D6690BCD0E}" name="gardenSize" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{19ADB5CF-92CB-4A31-B7EB-1EDD7240D840}" name="finishing" dataDxfId="19"/>
-    <tableColumn id="17" xr3:uid="{F6E56218-324E-4E12-A449-E3E0B9E0EFE9}" name="furnishing" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{D6BD6DF9-C3B6-466C-971B-0AFD6CBCD538}" name="garageArea" dataDxfId="17"/>
-    <tableColumn id="19" xr3:uid="{FC32A4C0-A4AA-48CE-BAF5-D17FFB9EB767}" name="images" dataDxfId="16"/>
-    <tableColumn id="20" xr3:uid="{2B4EB825-BF08-4696-903E-ABB2A4A89C6E}" name="code" dataDxfId="15"/>
-    <tableColumn id="21" xr3:uid="{6304F5B4-088C-43E1-B893-21EFF595D738}" name="model" dataDxfId="14"/>
-    <tableColumn id="22" xr3:uid="{65B95FA3-CF5A-4B4B-A77E-5EE23E88F4C0}" name="downPayment" dataDxfId="13"/>
-    <tableColumn id="23" xr3:uid="{517F21E8-2911-404F-8931-F26D3F835BF1}" name="totalPrice" dataDxfId="12"/>
-    <tableColumn id="24" xr3:uid="{75A6C596-4606-4846-BDF6-845A757383E2}" name="deliveryDate" dataDxfId="11"/>
-    <tableColumn id="26" xr3:uid="{E98C25B3-57C3-49F0-8C4A-BB22E43061F3}" name="pp2_price" dataDxfId="10"/>
-    <tableColumn id="27" xr3:uid="{B9027F89-E0B1-43E5-B52F-B85482B4E7A0}" name="pp2_maintenance" dataDxfId="9"/>
-    <tableColumn id="28" xr3:uid="{109A03A1-FCB4-47D8-A762-12BF24BE783E}" name="pp2_downPayment" dataDxfId="8"/>
-    <tableColumn id="29" xr3:uid="{56B61993-49B4-4525-9AD5-2BBEFADBD40E}" name="pp2_installment_amount_yearly" dataDxfId="7"/>
-    <tableColumn id="31" xr3:uid="{17BF8A49-67D8-40B5-95EC-DBBAC50B44E7}" name="pp5_price2" dataDxfId="6"/>
-    <tableColumn id="32" xr3:uid="{EE2E4F74-E083-4E3B-9403-4E3E8BA81EAA}" name="pp5_maintenance2" dataDxfId="5"/>
-    <tableColumn id="33" xr3:uid="{0CD16258-87B5-4A5D-A641-5EF15C94C8B5}" name="pp5_downPayment2" dataDxfId="4"/>
-    <tableColumn id="34" xr3:uid="{D36FFA32-EC49-4502-8158-1335A0DD0B15}" name="pp5_installment_amount_yearly2" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{39A43C69-BA8F-471A-820B-7634B6C00857}" name="project" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{FA20424E-B41B-418D-B6E2-BC001D54AF24}" name="project_ar" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{92AA78DB-91CF-4E52-AE17-54AF20AA84F3}" name="view" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{C686F568-A904-4F0F-B54B-0D41263C91E9}" name="phase" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{06DE9C09-9D66-4E84-8BFA-9250BFABA13D}" name="city" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{7C4AD4EF-299B-4722-8957-3F8D28742DEA}" name="district" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{C10A1A14-7EC1-45BC-9552-8A98401737DB}" name="developer" dataDxfId="24"/>
+    <tableColumn id="9" xr3:uid="{D8E6284D-A3D8-40F8-945D-91573DB99A46}" name="unitTitle" dataDxfId="23"/>
+    <tableColumn id="10" xr3:uid="{DF08E38D-EE22-40B8-B49B-AE8CFB132491}" name="deliveryStatus" dataDxfId="22"/>
+    <tableColumn id="11" xr3:uid="{8D57A761-E792-4EC1-8B0A-31C4AC71E587}" name="bathroomCount" dataDxfId="21"/>
+    <tableColumn id="12" xr3:uid="{4E64BA77-CE3B-4387-9005-D07472224E91}" name="floor" dataDxfId="20"/>
+    <tableColumn id="13" xr3:uid="{F3C7A4FD-240B-49B6-A0A9-F75B071F140D}" name="roomsCount" dataDxfId="19"/>
+    <tableColumn id="14" xr3:uid="{56F4F824-2572-46E3-8D06-031BA4492E81}" name="landArea" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{013500D4-906E-4C51-A6FC-49D6690BCD0E}" name="gardenSize" dataDxfId="17"/>
+    <tableColumn id="16" xr3:uid="{19ADB5CF-92CB-4A31-B7EB-1EDD7240D840}" name="finishing" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{F6E56218-324E-4E12-A449-E3E0B9E0EFE9}" name="furnishing" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{D6BD6DF9-C3B6-466C-971B-0AFD6CBCD538}" name="garageArea" dataDxfId="14"/>
+    <tableColumn id="19" xr3:uid="{FC32A4C0-A4AA-48CE-BAF5-D17FFB9EB767}" name="images" dataDxfId="13"/>
+    <tableColumn id="20" xr3:uid="{2B4EB825-BF08-4696-903E-ABB2A4A89C6E}" name="code" dataDxfId="12"/>
+    <tableColumn id="21" xr3:uid="{6304F5B4-088C-43E1-B893-21EFF595D738}" name="model" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{65B95FA3-CF5A-4B4B-A77E-5EE23E88F4C0}" name="downPayment" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{517F21E8-2911-404F-8931-F26D3F835BF1}" name="totalPrice" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{75A6C596-4606-4846-BDF6-845A757383E2}" name="deliveryDate" dataDxfId="8"/>
+    <tableColumn id="26" xr3:uid="{E98C25B3-57C3-49F0-8C4A-BB22E43061F3}" name="pp2_price" dataDxfId="7"/>
+    <tableColumn id="27" xr3:uid="{B9027F89-E0B1-43E5-B52F-B85482B4E7A0}" name="pp2_maintenance" dataDxfId="6"/>
+    <tableColumn id="28" xr3:uid="{109A03A1-FCB4-47D8-A762-12BF24BE783E}" name="pp2_downPayment" dataDxfId="5"/>
+    <tableColumn id="29" xr3:uid="{56B61993-49B4-4525-9AD5-2BBEFADBD40E}" name="pp2_installment_amount_yearly" dataDxfId="4"/>
+    <tableColumn id="31" xr3:uid="{17BF8A49-67D8-40B5-95EC-DBBAC50B44E7}" name="pp5_price2" dataDxfId="3"/>
+    <tableColumn id="32" xr3:uid="{EE2E4F74-E083-4E3B-9403-4E3E8BA81EAA}" name="pp5_maintenance2" dataDxfId="2"/>
+    <tableColumn id="33" xr3:uid="{0CD16258-87B5-4A5D-A641-5EF15C94C8B5}" name="pp5_downPayment2" dataDxfId="1"/>
+    <tableColumn id="34" xr3:uid="{D36FFA32-EC49-4502-8158-1335A0DD0B15}" name="pp5_installment_amount_yearly2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1941,16 +1935,16 @@
         <v>57</v>
       </c>
       <c r="AC1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD1" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE1" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
@@ -2008,9 +2002,7 @@
       <c r="R2" s="2">
         <v>0</v>
       </c>
-      <c r="S2" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="S2" s="2"/>
       <c r="T2" s="2" t="s">
         <v>13</v>
       </c>
@@ -2106,9 +2098,7 @@
       <c r="R3" s="3">
         <v>1</v>
       </c>
-      <c r="S3" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="S3" s="5"/>
       <c r="T3" s="3" t="s">
         <v>28</v>
       </c>
@@ -2196,9 +2186,7 @@
       <c r="R4" s="3">
         <v>0</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>58</v>
-      </c>
+      <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
         <v>13</v>
       </c>
@@ -2224,13 +2212,10 @@
       <c r="AF4" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="S3" r:id="rId1" xr:uid="{6F2E19E6-79A5-4B70-9830-FA8881310FA7}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/public/unit_upload_template.xlsx
+++ b/public/unit_upload_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\work\lenaAI\lenaai-website\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD1EA71-7A35-4B4B-8395-376E14F01C16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B700EFB-E625-4D82-91A1-E36924E136C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2832" yWindow="2832" windowWidth="22656" windowHeight="12120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>Lake View Apartment</t>
   </si>
   <si>
-    <t>ready</t>
-  </si>
-  <si>
     <t>semi finished</t>
   </si>
   <si>
@@ -206,6 +203,9 @@
   </si>
   <si>
     <t>pp5_installment_amount_yearly2</t>
+  </si>
+  <si>
+    <t>ready to move</t>
   </si>
 </sst>
 </file>
@@ -1854,97 +1854,97 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="X1" s="4" t="s">
+      <c r="Y1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="Y1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AA1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AA1" s="4" t="s">
+      <c r="AB1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AB1" s="4" t="s">
+      <c r="AC1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AC1" s="4" t="s">
+      <c r="AD1" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AD1" s="4" t="s">
+      <c r="AE1" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AE1" s="4" t="s">
+      <c r="AF1" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:32" ht="15.6" x14ac:dyDescent="0.3">
@@ -2072,7 +2072,7 @@
         <v>24</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="K3" s="3">
         <v>2</v>
@@ -2090,20 +2090,20 @@
         <v>20</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q3" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>27</v>
       </c>
       <c r="R3" s="3">
         <v>1</v>
       </c>
       <c r="S3" s="5"/>
       <c r="T3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>29</v>
       </c>
       <c r="V3" s="3">
         <v>500000</v>
@@ -2112,7 +2112,7 @@
         <v>4200000</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y3" s="3">
         <v>300000</v>
